--- a/src/data/PRODUCTOS_BASICOS_AUTO.xlsx
+++ b/src/data/PRODUCTOS_BASICOS_AUTO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\WebstormProjects\erpperu2-automation\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27933BB-7AB9-4134-9C56-88FA2384D6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DDD17F-0335-41D2-80F8-B406792F6F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32025" yWindow="3225" windowWidth="24000" windowHeight="10845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31590" yWindow="2790" windowWidth="24000" windowHeight="10845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="136">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -411,6 +411,33 @@
   </si>
   <si>
     <t>STOCK</t>
+  </si>
+  <si>
+    <t>STKPROD001</t>
+  </si>
+  <si>
+    <t>STKPROD002</t>
+  </si>
+  <si>
+    <t>STKPROD003</t>
+  </si>
+  <si>
+    <t>item edicion masivo stock auto</t>
+  </si>
+  <si>
+    <t>imte edicion de stock masivo flexible</t>
+  </si>
+  <si>
+    <t>item para la edicion de stock</t>
+  </si>
+  <si>
+    <t>EDICION</t>
+  </si>
+  <si>
+    <t>MASIVOS</t>
+  </si>
+  <si>
+    <t>AUTO</t>
   </si>
 </sst>
 </file>
@@ -650,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -686,6 +713,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1308,46 +1338,118 @@
       </c>
     </row>
     <row r="9" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="A9" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="16">
+        <v>10</v>
+      </c>
+      <c r="K9" s="15">
+        <v>10.5555</v>
+      </c>
+      <c r="L9" s="15">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="10" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
+      <c r="A10" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="16">
+        <v>10</v>
+      </c>
+      <c r="K10" s="15">
+        <v>10.5555</v>
+      </c>
+      <c r="L10" s="15">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="11" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
+      <c r="A11" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="16">
+        <v>10</v>
+      </c>
+      <c r="K11" s="15">
+        <v>10.5555</v>
+      </c>
+      <c r="L11" s="15">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="12" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
@@ -3033,7 +3135,7 @@
           <x14:formula1>
             <xm:f>DOMINIOS!$B$28:$B$43</xm:f>
           </x14:formula1>
-          <xm:sqref>I10:J130</xm:sqref>
+          <xm:sqref>I12:J130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/src/data/PRODUCTOS_BASICOS_AUTO.xlsx
+++ b/src/data/PRODUCTOS_BASICOS_AUTO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\WebstormProjects\erpperu2-automation\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DDD17F-0335-41D2-80F8-B406792F6F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F938D8-A477-4745-ABE6-9B5D40815B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31590" yWindow="2790" windowWidth="24000" windowHeight="10845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="136">
-  <si>
-    <t>DESCRIPCION</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="137">
   <si>
     <t>MARCA</t>
   </si>
@@ -438,6 +435,12 @@
   </si>
   <si>
     <t>AUTO</t>
+  </si>
+  <si>
+    <t>Item sin stock estricto</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
   </si>
 </sst>
 </file>
@@ -677,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -716,6 +719,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1037,40 +1041,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="6" customFormat="1" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>7</v>
-      </c>
       <c r="J1" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1078,28 +1082,28 @@
         <v>111111</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" t="s">
         <v>123</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>124</v>
       </c>
-      <c r="E2" t="s">
-        <v>125</v>
-      </c>
       <c r="F2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J2" s="16">
         <v>100</v>
@@ -1116,28 +1120,28 @@
         <v>121212</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
         <v>123</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>124</v>
       </c>
-      <c r="E3" t="s">
-        <v>125</v>
-      </c>
       <c r="F3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3" s="16">
         <v>100</v>
@@ -1154,28 +1158,28 @@
         <v>151515</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
         <v>123</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>124</v>
       </c>
-      <c r="E4" t="s">
-        <v>125</v>
-      </c>
       <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="H4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="15">
@@ -1190,28 +1194,28 @@
         <v>999999</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
         <v>123</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>124</v>
       </c>
-      <c r="E5" t="s">
-        <v>125</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" s="16">
         <v>10</v>
@@ -1228,28 +1232,28 @@
         <v>889988</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
         <v>123</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>124</v>
       </c>
-      <c r="E6" t="s">
-        <v>125</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" s="16">
         <v>10</v>
@@ -1266,28 +1270,28 @@
         <v>888999</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
         <v>123</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>124</v>
       </c>
-      <c r="E7" t="s">
-        <v>125</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J7" s="16">
         <v>10</v>
@@ -1304,28 +1308,28 @@
         <v>888888</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
         <v>122</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>123</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>124</v>
       </c>
-      <c r="E8" t="s">
-        <v>125</v>
-      </c>
       <c r="F8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J8" s="16">
         <v>10</v>
@@ -1339,31 +1343,31 @@
     </row>
     <row r="9" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" t="s">
         <v>133</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>134</v>
       </c>
-      <c r="E9" t="s">
-        <v>135</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I9" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" s="16">
         <v>10</v>
@@ -1377,31 +1381,31 @@
     </row>
     <row r="10" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" t="s">
         <v>133</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>134</v>
       </c>
-      <c r="E10" t="s">
-        <v>135</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J10" s="16">
         <v>10</v>
@@ -1415,31 +1419,31 @@
     </row>
     <row r="11" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
         <v>132</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>133</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>134</v>
       </c>
-      <c r="E11" t="s">
-        <v>135</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I11" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J11" s="16">
         <v>10</v>
@@ -1452,18 +1456,40 @@
       </c>
     </row>
     <row r="12" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+      <c r="A12" s="7">
+        <v>111222</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="J12" s="16"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
+      <c r="K12" s="15">
+        <v>10</v>
+      </c>
+      <c r="L12" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
@@ -1519,7 +1545,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="18"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
@@ -3135,7 +3161,7 @@
           <x14:formula1>
             <xm:f>DOMINIOS!$B$28:$B$43</xm:f>
           </x14:formula1>
-          <xm:sqref>I12:J130</xm:sqref>
+          <xm:sqref>J12:J130 I13:I130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3154,542 +3180,542 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B117" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B121" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B123" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/PRODUCTOS_BASICOS_AUTO.xlsx
+++ b/src/data/PRODUCTOS_BASICOS_AUTO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\WebstormProjects\erpperu2-automation\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F938D8-A477-4745-ABE6-9B5D40815B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC73A8A9-92EB-4EF7-9B3D-357124C5673E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
